--- a/terminology/CodeSystem-allergy-intolerance-criticality-cz.xlsx
+++ b/terminology/CodeSystem-allergy-intolerance-criticality-cz.xlsx
@@ -30,13 +30,13 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>AllergyIntoleranceCriticality</t>
+    <t>AllergyIntoleranceCriticalityCz</t>
   </si>
   <si>
     <t>Title</t>
